--- a/MiniTemplate/Datas/buffConfig.xlsx
+++ b/MiniTemplate/Datas/buffConfig.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -443,25 +443,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:Q34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col width="8.5546875" bestFit="1" customWidth="1" min="1" max="2"/>
-    <col width="13.88671875" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="44.6640625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="9.5546875" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="40.21875" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="24.88671875" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="47.88671875" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="30.33203125" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="22.6640625" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="10.5546875" bestFit="1" customWidth="1" min="11" max="11"/>
-    <col width="50.109375" bestFit="1" customWidth="1" min="12" max="12"/>
-    <col width="20.44140625" bestFit="1" customWidth="1" min="13" max="13"/>
-    <col width="131.33203125" bestFit="1" customWidth="1" min="14" max="14"/>
-    <col width="39.109375" bestFit="1" customWidth="1" min="15" max="15"/>
-    <col width="36.88671875" bestFit="1" customWidth="1" min="16" max="16"/>
-    <col width="33.6640625" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="8.5" bestFit="1" customWidth="1" min="1" max="2"/>
+    <col width="13.875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="44.625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="9.5" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="40.25" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="24.875" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="47.875" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="30.375" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="22.625" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="10.5" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="50.125" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="20.5" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="131.375" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="39.125" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="36.875" bestFit="1" customWidth="1" min="16" max="16"/>
+    <col width="33.625" bestFit="1" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -818,12 +818,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>状态很好</t>
+          <t>财运到</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>零工模拟币收益提高 20%，持续两回合</t>
+          <t>零工模拟币收益提高 10%，持续两回合</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -876,7 +876,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>零工体力消耗降低 20%，可叠加至三层</t>
+          <t>体力消耗降低 20%，可叠加至三层</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -920,16 +920,16 @@
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>1003</v>
+        <v>2001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>居住舒适</t>
+          <t>社区热心肠 I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>满意度达到 20 时，零工模拟币收益提高 10%</t>
+          <t>社区经验 +5%</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -956,33 +956,36 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>RefreshDuration</t>
+          <t>Replace</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>WorkCoinMultiplier</t>
+          <t>CommunityExperienceMultiplier</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>学习经验 I</t>
+          <t>社区热心肠 II</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>学习经验 +8%</t>
+          <t>社区经验 +10%</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1017,11 +1020,11 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>LearningExperienceMultiplier</t>
+          <t>CommunityExperienceMultiplier</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1029,16 +1032,16 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>学习经验 II</t>
+          <t>社区热心肠 III</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>学习经验 +16%</t>
+          <t>社区经验 +15%</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1073,11 +1076,11 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>LearningExperienceMultiplier</t>
+          <t>CommunityExperienceMultiplier</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1085,16 +1088,16 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>学习经验 III</t>
+          <t>商店增益 I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>学习经验 +25%</t>
+          <t>商品价格 -1%</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1129,11 +1132,11 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>LearningExperienceMultiplier</t>
+          <t>ShopPriceMultiplier</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0.25</v>
+        <v>-0.01</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1141,16 +1144,16 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>商店增益 I</t>
+          <t>商店增益 II</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>商品价格 -3%</t>
+          <t>商品价格 -2%</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1189,7 +1192,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1197,16 +1200,16 @@
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>商店增益 II</t>
+          <t>商店增益 III</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>商品价格 -6%</t>
+          <t>商品价格 -3%</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1245,7 +1248,7 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1253,16 +1256,16 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>商店增益 III</t>
+          <t>邻里机遇 I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>商品价格 -10%</t>
+          <t>正面机遇权重 ×1.12</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1297,11 +1300,11 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>ShopPriceMultiplier</t>
+          <t>PositiveEncounterWeightMultiplier</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>-0.1</v>
+        <v>0.12</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1309,16 +1312,16 @@
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>邻里机遇 I</t>
+          <t>邻里机遇 II</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>正面机遇权重 ×1.12</t>
+          <t>正面机遇权重 ×1.25，机遇奖励 +5%</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1357,24 +1360,29 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>PositiveEncounterRewardMultiplier</t>
+        </is>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>邻里机遇 II</t>
+          <t>邻里机遇 III</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>正面机遇权重 ×1.25，机遇奖励 +5%</t>
+          <t>正面机遇权重 ×1.40，机遇奖励 +10%</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1413,7 +1421,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1421,21 +1429,21 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>邻里机遇 III</t>
+          <t>零工收益 I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>正面机遇权重 ×1.40，机遇奖励 +10%</t>
+          <t>零工模拟币 +5%</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1470,33 +1478,28 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>PositiveEncounterWeightMultiplier</t>
+          <t>WorkCoinMultiplier</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>PositiveEncounterRewardMultiplier</t>
-        </is>
+        <v>0.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>零工收益 I</t>
+          <t>零工收益 II</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>零工模拟币 +5%</t>
+          <t>零工模拟币 +10%</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1535,7 +1538,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1543,16 +1546,16 @@
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>零工收益 II</t>
+          <t>零工收益 III</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>零工模拟币 +10%</t>
+          <t>零工模拟币 +18%</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1591,7 +1594,7 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1599,16 +1602,16 @@
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>零工收益 III</t>
+          <t>健康增益 I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>零工模拟币 +18%</t>
+          <t>治疗及药物恢复量 +10%</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1643,11 +1646,11 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>WorkCoinMultiplier</t>
+          <t>TreatmentAndDrugEffectMultiplier</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -1655,16 +1658,16 @@
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>健康增益 I</t>
+          <t>健康增益 II</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>治疗及药物恢复量 +10%</t>
+          <t>治疗及药物恢复量 +20%，治疗费用 -5%</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1703,24 +1706,29 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>TreatmentCostMultiplier</t>
+        </is>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>健康增益 II</t>
+          <t>健康增益 III</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>治疗及药物恢复量 +20%，治疗费用 -5%</t>
+          <t>治疗及药物恢复量 +30%，治疗费用 -10%</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1759,7 +1767,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -1767,21 +1775,21 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>健康增益 III</t>
+          <t>抽奖概率 I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>治疗及药物恢复量 +30%，治疗费用 -10%</t>
+          <t>稀有奖励权重 ×1.08</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1816,33 +1824,28 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>TreatmentAndDrugEffectMultiplier</t>
+          <t>RareLotteryRewardWeightMultiplier</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>TreatmentCostMultiplier</t>
-        </is>
+        <v>0.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>抽奖概率 I</t>
+          <t>抽奖概率 II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>稀有奖励权重 ×1.08</t>
+          <t>稀有奖励权重 ×1.16</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1881,7 +1884,7 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -1889,16 +1892,16 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>抽奖概率 II</t>
+          <t>抽奖概率 III</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>稀有奖励权重 ×1.16</t>
+          <t>稀有奖励权重 ×1.28</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1937,7 +1940,7 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -1945,16 +1948,16 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>2018</v>
+        <v>3001</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>抽奖概率 III</t>
+          <t>温馨起居 I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>稀有奖励权重 ×1.28</t>
+          <t>零工收益 +2%</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1962,7 +1965,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>HomeSatisfaction</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1989,11 +1992,11 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>RareLotteryRewardWeightMultiplier</t>
+          <t>WorkCoinMultiplier</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>0.28</v>
+        <v>0.02</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2001,16 +2004,16 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>温馨起居 I</t>
+          <t>垂钓资格</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>零工收益 +2%</t>
+          <t>解锁钓鱼</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2045,11 +2048,11 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>WorkCoinMultiplier</t>
+          <t>UnlockFishing</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2057,16 +2060,16 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>精打细算 I</t>
+          <t>垂钓闲趣 I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>商品价格 -2%</t>
+          <t>钓鱼进度 +10%</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2101,11 +2104,11 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>ShopPriceMultiplier</t>
+          <t>FishCatchProgressMultiplier</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>-0.02</v>
+        <v>0.1</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2113,16 +2116,16 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>垂钓闲趣 I</t>
+          <t>高效生活 I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>钓鱼进度 +10%</t>
+          <t>零工收益 +5%</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2157,11 +2160,11 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>FishCatchProgressMultiplier</t>
+          <t>WorkCoinMultiplier</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2169,16 +2172,16 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>高效生活 I</t>
+          <t>精打细算 II</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>零工收益 +5%</t>
+          <t>商品价格 -5%</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2213,11 +2216,11 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>WorkCoinMultiplier</t>
+          <t>ShopPriceMultiplier</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2225,16 +2228,16 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>精打细算 II</t>
+          <t>垂钓闲趣 II</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>商品价格 -5%</t>
+          <t>钓鱼进度 +20%</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2269,11 +2272,11 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>ShopPriceMultiplier</t>
+          <t>FishCatchProgressMultiplier</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>-0.05</v>
+        <v>0.2</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2281,16 +2284,16 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>垂钓闲趣 II</t>
+          <t>神秘转盘</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>钓鱼进度 +20%</t>
+          <t>解锁神秘转盘</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2325,11 +2328,11 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>FishCatchProgressMultiplier</t>
+          <t>UnlockMysteryWheelLottery</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2337,16 +2340,16 @@
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>3007</v>
+        <v>3008</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>神秘转盘</t>
+          <t>精打细算 III</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>解锁神秘转盘</t>
+          <t>商品价格 -10%</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2381,11 +2384,11 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>UnlockMysteryWheelLottery</t>
+          <t>ShopPriceMultiplier</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>-0.1</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -2393,16 +2396,16 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>3008</v>
+        <v>3009</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>精打细算 III</t>
+          <t>时光秘匣</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>商品价格 -10%</t>
+          <t>解锁宝箱抽奖</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2437,11 +2440,11 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>ShopPriceMultiplier</t>
+          <t>UnlockBoxLottery</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>-0.1</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -2449,16 +2452,16 @@
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>3009</v>
+        <v>3010</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>时光秘匣</t>
+          <t>时光星阵</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>解锁宝箱抽奖</t>
+          <t>解锁卡牌抽奖，零工收益 +20%</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -2493,74 +2496,18 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>UnlockBoxLottery</t>
+          <t>UnlockCardLottery</t>
         </is>
       </c>
       <c r="O34" t="n">
         <v>1</v>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>WorkCoinMultiplier</t>
+        </is>
+      </c>
       <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="n">
-        <v>3010</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>时光星阵</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>解锁卡牌抽奖，零工收益 +20%</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>HomeSatisfaction</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Permanent</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Replace</t>
-        </is>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>UnlockCardLottery</t>
-        </is>
-      </c>
-      <c r="O35" t="n">
-        <v>1</v>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>WorkCoinMultiplier</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
         <v>0.2</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/buffConfig.xlsx
+++ b/MiniTemplate/Datas/buffConfig.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="8.5" bestFit="1" customWidth="1" min="1" max="2"/>
@@ -864,16 +864,16 @@
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>2001</v>
+        <v>1003</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>社区热心肠 I</t>
+          <t>过度疲劳</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>社区经验 +5%</t>
+          <t>体力消耗增加 20%，持续两回合</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>HealthBelowThreshold</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -889,22 +889,22 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Permanent</t>
+          <t>Turns</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CommunityExperienceMultiplier</t>
+          <t>WorkHealthCostMultiplier</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -912,16 +912,16 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>社区热心肠 II</t>
+          <t>社区热心肠 I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>社区经验 +10%</t>
+          <t>社区经验 +5%</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -960,16 +960,16 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>社区热心肠 III</t>
+          <t>社区热心肠 II</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>社区经验 +15%</t>
+          <t>社区经验 +10%</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1008,16 +1008,16 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>优惠促销 I</t>
+          <t>社区热心肠 III</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>家具和便利店商品价格 -1%</t>
+          <t>社区经验 +15%</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1044,11 +1044,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ShopPriceMultiplier</t>
+          <t>CommunityExperienceMultiplier</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>-0.01</v>
+        <v>0.15</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1056,16 +1056,16 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>优惠促销 II</t>
+          <t>优惠促销 I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>家具和便利店商品价格 -2%</t>
+          <t>家具和便利店商品价格 -1%</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1104,16 +1104,16 @@
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>优惠促销 III</t>
+          <t>优惠促销 II</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>家具和便利店商品价格 -3%</t>
+          <t>家具和便利店商品价格 -2%</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1152,16 +1152,16 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>邻里机遇 I</t>
+          <t>优惠促销 III</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>正面机遇权重 ×1.12</t>
+          <t>家具和便利店商品价格 -3%</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1188,11 +1188,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PositiveEncounterWeightMultiplier</t>
+          <t>ShopPriceMultiplier</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1200,16 +1200,16 @@
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>邻里机遇 II</t>
+          <t>邻里机遇 I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>正面机遇权重 ×1.25，机遇奖励 +5%</t>
+          <t>正面机遇权重 ×1.12</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1240,29 +1240,24 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>PositiveEncounterRewardMultiplier</t>
-        </is>
+        <v>0.12</v>
       </c>
       <c r="O14" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>邻里机遇 III</t>
+          <t>邻里机遇 II</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>正面机遇权重 ×1.40，机遇奖励 +10%</t>
+          <t>正面机遇权重 ×1.25，机遇奖励 +5%</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1293,7 +1288,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1301,21 +1296,21 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>零工收益 I</t>
+          <t>邻里机遇 III</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>零工模拟币 +5%</t>
+          <t>正面机遇权重 ×1.40，机遇奖励 +10%</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1342,28 +1337,33 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>WorkCoinMultiplier</t>
+          <t>PositiveEncounterWeightMultiplier</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.05</v>
+        <v>0.4</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>PositiveEncounterRewardMultiplier</t>
+        </is>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>零工收益 II</t>
+          <t>零工收益 I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>零工模拟币 +10%</t>
+          <t>零工模拟币 +5%</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1402,16 +1402,16 @@
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>零工收益 III</t>
+          <t>零工收益 II</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>零工模拟币 +18%</t>
+          <t>零工模拟币 +10%</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -1450,16 +1450,16 @@
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>健康增益 I</t>
+          <t>零工收益 III</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>治疗及药物恢复量 +10%</t>
+          <t>零工模拟币 +18%</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1486,11 +1486,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>TreatmentAndDrugEffectMultiplier</t>
+          <t>WorkCoinMultiplier</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -1498,16 +1498,16 @@
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>健康增益 II</t>
+          <t>健康增益 I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>治疗及药物恢复量 +20%，治疗费用 -5%</t>
+          <t>治疗及药物恢复量 +10%</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1538,29 +1538,24 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>TreatmentCostMultiplier</t>
-        </is>
+        <v>0.1</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>健康增益 III</t>
+          <t>健康增益 II</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>治疗及药物恢复量 +30%，治疗费用 -10%</t>
+          <t>治疗及药物恢复量 +20%，治疗费用 -5%</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1591,7 +1586,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1599,21 +1594,21 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>-0.1</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>抽奖概率 I</t>
+          <t>健康增益 III</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>稀有奖励权重 ×1.08</t>
+          <t>治疗及药物恢复量 +30%，治疗费用 -10%</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1640,28 +1635,33 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>RareLotteryRewardWeightMultiplier</t>
+          <t>TreatmentAndDrugEffectMultiplier</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.08</v>
+        <v>0.3</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>TreatmentCostMultiplier</t>
+        </is>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>抽奖概率 II</t>
+          <t>抽奖概率 I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>稀有奖励权重 ×1.16</t>
+          <t>稀有奖励权重 ×1.08</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -1700,16 +1700,16 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>抽奖概率 III</t>
+          <t>抽奖概率 II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>稀有奖励权重 ×1.28</t>
+          <t>稀有奖励权重 ×1.16</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -1748,16 +1748,16 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>3001</v>
+        <v>2018</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>温馨起居 I</t>
+          <t>抽奖概率 III</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>零工收益 +2%</t>
+          <t>稀有奖励权重 ×1.28</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HomeSatisfaction</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1784,11 +1784,11 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>WorkCoinMultiplier</t>
+          <t>RareLotteryRewardWeightMultiplier</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.02</v>
+        <v>0.28</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -1796,16 +1796,16 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>垂钓资格</t>
+          <t>温馨起居 I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>解锁钓鱼</t>
+          <t>零工收益 +2%</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1832,11 +1832,11 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>UnlockFishing</t>
+          <t>WorkCoinMultiplier</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -1844,16 +1844,16 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>活力生活 I</t>
+          <t>垂钓资格</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>体力消耗 -10%</t>
+          <t>解锁钓鱼</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1880,11 +1880,11 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>WorkHealthCostMultiplier</t>
+          <t>UnlockFishing</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>-0.1</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -1892,16 +1892,16 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>隐藏任务</t>
+          <t>活力生活 I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>开启隐藏任务海洋之心</t>
+          <t>体力消耗 -10%</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1926,8 +1926,13 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>WorkHealthCostMultiplier</t>
+        </is>
+      </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -1935,16 +1940,16 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>精打细算 II</t>
+          <t>隐藏任务</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>商品价格 -5%</t>
+          <t>开启隐藏任务海洋之心</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1969,13 +1974,8 @@
       <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>ShopPriceMultiplier</t>
-        </is>
-      </c>
       <c r="M29" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -1983,16 +1983,16 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>垂钓闲趣 II</t>
+          <t>沿江港口</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>钓鱼进度 +20%</t>
+          <t>解锁沿江港口</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2019,11 +2019,11 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>FishCatchProgressMultiplier</t>
+          <t>UnlockPort</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -2031,16 +2031,16 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>神秘转盘</t>
+          <t>垂钓闲趣 II</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>解锁神秘转盘</t>
+          <t>钓鱼进度 +20%</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2067,11 +2067,11 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>UnlockMysteryWheelLottery</t>
+          <t>FishCatchProgressMultiplier</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -2079,16 +2079,16 @@
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>精打细算 III</t>
+          <t>神秘转盘</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>商品价格 -10%</t>
+          <t>解锁神秘转盘</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2115,11 +2115,11 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ShopPriceMultiplier</t>
+          <t>UnlockMysteryWheelLottery</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-0.1</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>时光秘匣</t>
+          <t>精打细算 III</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>解锁宝箱抽奖</t>
+          <t>商品价格 -10%</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2163,11 +2163,11 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>UnlockBoxLottery</t>
+          <t>ShopPriceMultiplier</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>-0.1</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -2175,16 +2175,16 @@
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>时光星阵</t>
+          <t>时光秘匣</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>解锁卡牌抽奖，零工收益 +20%</t>
+          <t>解锁宝箱抽奖</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -2211,18 +2211,66 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>UnlockCardLottery</t>
+          <t>UnlockBoxLottery</t>
         </is>
       </c>
       <c r="M34" t="n">
         <v>1</v>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>3010</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>时光星阵</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>解锁卡牌抽奖，零工收益 +20%</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>HomeSatisfaction</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>UnlockCardLottery</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>WorkCoinMultiplier</t>
         </is>
       </c>
-      <c r="O34" t="n">
+      <c r="O35" t="n">
         <v>0.2</v>
       </c>
     </row>
